--- a/BeatnotePostHotCellF1=4/Jul14,2026/Fit_ResultJun14.xlsx
+++ b/BeatnotePostHotCellF1=4/Jul14,2026/Fit_ResultJun14.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\BeatnotePostHotCellF1=4\Jul14,2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E15C2676-FA94-4955-BDAB-41C0667BAF4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{042E7298-5650-4423-B937-D6087930ECDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{D9E101C5-8284-4B59-8B1C-2AD2D5F2FDD3}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="33">
   <si>
     <t>Date</t>
   </si>
@@ -138,9 +138,6 @@
   </si>
   <si>
     <t>Jul14,2026+6-16-24PM</t>
-  </si>
-  <si>
-    <t>Jul14,2026+1-36-36PM</t>
   </si>
 </sst>
 </file>
@@ -1282,603 +1279,587 @@
     </row>
     <row r="2" spans="1:20" ht="42.75">
       <c r="A2" s="1" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1">
-        <v>0.10815404389771199</v>
+        <v>8.4098670481367904E-2</v>
       </c>
       <c r="C2" s="1">
-        <v>1.64332883279856</v>
+        <v>1.64478856225619</v>
       </c>
       <c r="D2" s="1">
-        <v>1.00832413866825E-3</v>
+        <v>3.64161951644183E-4</v>
       </c>
       <c r="E2" s="1">
-        <v>-2.43578774701861E-4</v>
+        <v>-1.07092210740408E-4</v>
       </c>
       <c r="F2" s="1">
-        <v>2.6468610341861898</v>
+        <v>2.5953388866566098</v>
       </c>
       <c r="G2" s="1">
-        <v>42.081233685446399</v>
+        <v>41.062704013428601</v>
       </c>
       <c r="H2" s="1">
-        <v>6.7477454252833102E-4</v>
+        <v>7.5220928414246302E-4</v>
       </c>
       <c r="L2" s="1"/>
     </row>
     <row r="3" spans="1:20" ht="42.75">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1">
-        <v>0.107867853594575</v>
+        <v>8.3770582022428597E-2</v>
       </c>
       <c r="C3" s="1">
-        <v>1.64478856225619</v>
+        <v>1.64375172643706</v>
       </c>
       <c r="D3" s="1">
-        <v>3.64161951644183E-4</v>
+        <v>6.4264841234899198E-4</v>
       </c>
       <c r="E3" s="1">
-        <v>-1.07092210740408E-4</v>
+        <v>-1.17206953457526E-4</v>
       </c>
       <c r="F3" s="1">
-        <v>2.6565544663029099</v>
+        <v>2.5838341434076102</v>
       </c>
       <c r="G3" s="1">
-        <v>40.085005947036699</v>
+        <v>40.094337592797203</v>
       </c>
       <c r="H3" s="1">
-        <v>6.3453421773680696E-4</v>
+        <v>5.7932144340976902E-4</v>
       </c>
       <c r="L3" s="1"/>
     </row>
     <row r="4" spans="1:20" ht="42.75">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1">
-        <v>0.107552731189269</v>
+        <v>8.3930571430078399E-2</v>
       </c>
       <c r="C4" s="1">
-        <v>1.64375172643706</v>
+        <v>1.6438518350140801</v>
       </c>
       <c r="D4" s="1">
-        <v>6.4264841234899198E-4</v>
+        <v>5.2459095729422698E-4</v>
       </c>
       <c r="E4" s="1">
-        <v>-1.17206953457526E-4</v>
+        <v>-1.064144168145E-4</v>
       </c>
       <c r="F4" s="1">
-        <v>2.6450232542828398</v>
+        <v>2.08570735335819</v>
       </c>
       <c r="G4" s="1">
-        <v>40.134314366191099</v>
+        <v>41.0016955036198</v>
       </c>
       <c r="H4" s="1">
-        <v>5.7944829645124895E-4</v>
+        <v>5.7949861781105396E-4</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="42.75">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1">
-        <v>0.10779387708665</v>
+        <v>8.4386871474939104E-2</v>
       </c>
       <c r="C5" s="1">
-        <v>1.6438518350140801</v>
+        <v>1.6438635171427001</v>
       </c>
       <c r="D5" s="1">
-        <v>5.2459095729422698E-4</v>
+        <v>1.1949072038449601E-3</v>
       </c>
       <c r="E5" s="1">
-        <v>-1.064144168145E-4</v>
+        <v>-2.8096089493189098E-4</v>
       </c>
       <c r="F5" s="1">
-        <v>2.1469272399174999</v>
+        <v>2.3318018965723999</v>
       </c>
       <c r="G5" s="1">
-        <v>41.085397669116603</v>
+        <v>41.103184008222101</v>
       </c>
       <c r="H5" s="1">
-        <v>7.5220773038939097E-4</v>
+        <v>7.5220848675051997E-4</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="42.75">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1">
-        <v>0.108339047437144</v>
+        <v>8.3779094698236606E-2</v>
       </c>
       <c r="C6" s="1">
-        <v>1.6438635171427001</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1.1949072038449601E-3</v>
-      </c>
-      <c r="E6" s="1">
-        <v>-2.8096089493189098E-4</v>
+        <v>1.64360592658481</v>
+      </c>
+      <c r="D6" s="2">
+        <v>4.0102241682057698E-5</v>
+      </c>
+      <c r="E6" s="2">
+        <v>3.48406710711816E-5</v>
       </c>
       <c r="F6" s="1">
-        <v>2.39301439825448</v>
+        <v>2.58639363333858</v>
       </c>
       <c r="G6" s="1">
-        <v>41.103178623093797</v>
+        <v>40.0633165988096</v>
       </c>
       <c r="H6" s="1">
-        <v>7.5220700358360798E-4</v>
+        <v>6.0220900707829296E-4</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="42.75">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1">
-        <v>0.107577120583375</v>
+        <v>8.4368245251587398E-2</v>
       </c>
       <c r="C7" s="1">
-        <v>1.64360592658481</v>
-      </c>
-      <c r="D7" s="2">
-        <v>4.0102241682057698E-5</v>
-      </c>
-      <c r="E7" s="2">
-        <v>3.48406710711816E-5</v>
+        <v>1.64549111708333</v>
+      </c>
+      <c r="D7" s="1">
+        <v>8.3767737234240701E-4</v>
+      </c>
+      <c r="E7" s="1">
+        <v>-1.15605532694043E-4</v>
       </c>
       <c r="F7" s="1">
-        <v>2.6475916789135998</v>
+        <v>2.0824996988656501</v>
       </c>
       <c r="G7" s="1">
-        <v>40.071470668469502</v>
+        <v>41.121438530205303</v>
       </c>
       <c r="H7" s="1">
-        <v>6.8748496725860397E-4</v>
+        <v>7.5220876002920795E-4</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="42.75">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1">
-        <v>0.108317067772985</v>
+        <v>8.4640740114124396E-2</v>
       </c>
       <c r="C8" s="1">
-        <v>1.64549111708333</v>
+        <v>1.6451122453700899</v>
       </c>
       <c r="D8" s="1">
-        <v>8.3767737234240701E-4</v>
+        <v>1.57682245400838E-3</v>
       </c>
       <c r="E8" s="1">
-        <v>-1.15605532694043E-4</v>
+        <v>-2.5029787686810403E-4</v>
       </c>
       <c r="F8" s="1">
-        <v>2.1436858339437599</v>
+        <v>2.5849268307502302</v>
       </c>
       <c r="G8" s="1">
-        <v>41.121434429279901</v>
+        <v>41.0552770964483</v>
       </c>
       <c r="H8" s="1">
-        <v>7.5220801223576598E-4</v>
+        <v>1.1554586775848301E-3</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="42.75">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1">
-        <v>0.108753685676204</v>
+        <v>8.3819572528152295E-2</v>
       </c>
       <c r="C9" s="1">
-        <v>1.6451122453700899</v>
+        <v>1.64530569142216</v>
       </c>
       <c r="D9" s="1">
-        <v>1.57682245400838E-3</v>
-      </c>
-      <c r="E9" s="1">
-        <v>-2.5029787686810403E-4</v>
+        <v>5.0073877493836698E-4</v>
+      </c>
+      <c r="E9" s="2">
+        <v>-4.82624570468744E-5</v>
       </c>
       <c r="F9" s="1">
-        <v>2.6461393264815301</v>
+        <v>2.3344672337013499</v>
       </c>
       <c r="G9" s="1">
-        <v>42.1691316214878</v>
+        <v>40.181528142376798</v>
       </c>
       <c r="H9" s="1">
-        <v>1.15683763418853E-3</v>
+        <v>5.9899589973342498E-4</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="42.75">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" s="1">
-        <v>0.107673177325291</v>
+        <v>8.4298501986348195E-2</v>
       </c>
       <c r="C10" s="1">
-        <v>1.64530569142216</v>
+        <v>1.64599711556128</v>
       </c>
       <c r="D10" s="1">
-        <v>5.0073877493836698E-4</v>
-      </c>
-      <c r="E10" s="2">
-        <v>-4.82624570468744E-5</v>
+        <v>6.6044105162320701E-4</v>
+      </c>
+      <c r="E10" s="1">
+        <v>-1.1395057196655E-4</v>
       </c>
       <c r="F10" s="1">
-        <v>2.3956679336241402</v>
+        <v>2.0443807307852402</v>
       </c>
       <c r="G10" s="1">
-        <v>41.018808567783701</v>
+        <v>41.167858890003302</v>
       </c>
       <c r="H10" s="1">
-        <v>5.92467625058586E-4</v>
+        <v>7.5220890023862798E-4</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="42.75">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" s="1">
-        <v>0.108229705876452</v>
+        <v>8.3749879844150901E-2</v>
       </c>
       <c r="C11" s="1">
-        <v>1.64599711556128</v>
+        <v>1.64523333775044</v>
       </c>
       <c r="D11" s="1">
-        <v>6.6044105162320701E-4</v>
+        <v>9.5475402057164805E-4</v>
       </c>
       <c r="E11" s="1">
-        <v>-1.1395057196655E-4</v>
+        <v>-1.28546304102757E-4</v>
       </c>
       <c r="F11" s="1">
-        <v>2.10556867745693</v>
+        <v>2.5845105893129001</v>
       </c>
       <c r="G11" s="1">
-        <v>41.167851355476301</v>
+        <v>40.494313683786899</v>
       </c>
       <c r="H11" s="1">
-        <v>7.5220794316968804E-4</v>
+        <v>5.9241636824247602E-4</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="42.75">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1">
-        <v>0.10760496944564001</v>
+        <v>8.4288203419773597E-2</v>
       </c>
       <c r="C12" s="1">
-        <v>1.64523333775044</v>
+        <v>1.64680033631321</v>
       </c>
       <c r="D12" s="1">
-        <v>9.5475402057164805E-4</v>
+        <v>6.1358709855903796E-4</v>
       </c>
       <c r="E12" s="1">
-        <v>-1.28546304102757E-4</v>
+        <v>-1.07580174048207E-4</v>
       </c>
       <c r="F12" s="1">
-        <v>2.6457180729062499</v>
+        <v>1.8349067635355301</v>
       </c>
       <c r="G12" s="1">
-        <v>41.189665193185299</v>
+        <v>41.168176781999797</v>
       </c>
       <c r="H12" s="1">
-        <v>7.52208121285431E-4</v>
+        <v>7.5220903163623995E-4</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="42.75">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1">
-        <v>0.108210284447238</v>
+        <v>8.4433783424020706E-2</v>
       </c>
       <c r="C13" s="1">
-        <v>1.64680033631321</v>
+        <v>1.6487901876461899</v>
       </c>
       <c r="D13" s="1">
-        <v>6.1358709855903796E-4</v>
+        <v>5.6414786462253999E-4</v>
       </c>
       <c r="E13" s="1">
-        <v>-1.07580174048207E-4</v>
+        <v>-1.6585793435037999E-4</v>
       </c>
       <c r="F13" s="1">
-        <v>1.89610798085453</v>
+        <v>1.7945669987369299</v>
       </c>
       <c r="G13" s="1">
-        <v>41.168194603460798</v>
+        <v>41.225370963954703</v>
       </c>
       <c r="H13" s="1">
-        <v>7.5221189799092503E-4</v>
+        <v>7.5220864834191496E-4</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="42.75">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14" s="1">
-        <v>0.108391645730674</v>
+        <v>8.3978129655986694E-2</v>
       </c>
       <c r="C14" s="1">
-        <v>1.6487901876461899</v>
+        <v>1.6490129792353601</v>
       </c>
       <c r="D14" s="1">
-        <v>5.6414786462253999E-4</v>
+        <v>1.9609170843340999E-4</v>
       </c>
       <c r="E14" s="1">
-        <v>-1.6585793435037999E-4</v>
+        <v>-1.0808752506353099E-4</v>
       </c>
       <c r="F14" s="1">
-        <v>1.8557775180474001</v>
+        <v>1.5844237017781799</v>
       </c>
       <c r="G14" s="1">
-        <v>41.225378184466102</v>
+        <v>40.232987045046102</v>
       </c>
       <c r="H14" s="1">
-        <v>7.5220828564758098E-4</v>
+        <v>6.9718479552250605E-4</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="42.75">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B15" s="1">
-        <v>0.10781058117576001</v>
+        <v>8.4391376865179599E-2</v>
       </c>
       <c r="C15" s="1">
-        <v>1.6490129792353601</v>
+        <v>1.6486723867456601</v>
       </c>
       <c r="D15" s="1">
-        <v>1.9609170843340999E-4</v>
+        <v>1.0157208622746099E-3</v>
       </c>
       <c r="E15" s="1">
-        <v>-1.0808752506353099E-4</v>
+        <v>-3.0323598547079899E-4</v>
       </c>
       <c r="F15" s="1">
-        <v>1.64563597409991</v>
+        <v>1.5852110921898299</v>
       </c>
       <c r="G15" s="1">
-        <v>40.433571603476103</v>
+        <v>41.821265591546499</v>
       </c>
       <c r="H15" s="1">
-        <v>5.9612073204901104E-4</v>
+        <v>8.5748047949138202E-4</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="42.75">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16" s="1">
-        <v>0.108326143627196</v>
+        <v>8.3986778727553404E-2</v>
       </c>
       <c r="C16" s="1">
-        <v>1.6486723867456601</v>
+        <v>1.6490531459587201</v>
       </c>
       <c r="D16" s="1">
-        <v>1.0157208622746099E-3</v>
+        <v>4.4144959800554201E-4</v>
       </c>
       <c r="E16" s="1">
-        <v>-3.0323598547079899E-4</v>
+        <v>-1.6744467044187001E-4</v>
       </c>
       <c r="F16" s="1">
-        <v>1.6464095556370999</v>
+        <v>2.08478416965696</v>
       </c>
       <c r="G16" s="1">
-        <v>41.612294628196203</v>
+        <v>41.1875339856146</v>
       </c>
       <c r="H16" s="1">
-        <v>8.7880534367463896E-4</v>
+        <v>7.5220800201283302E-4</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="42.75">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B17" s="1">
-        <v>0.107921570762375</v>
+        <v>8.3700704517771493E-2</v>
       </c>
       <c r="C17" s="1">
-        <v>1.6490531459587201</v>
+        <v>1.6481192218492899</v>
       </c>
       <c r="D17" s="1">
-        <v>4.4144959800554201E-4</v>
+        <v>6.04689558055987E-4</v>
       </c>
       <c r="E17" s="1">
-        <v>-1.6744467044187001E-4</v>
+        <v>-1.4610146508219399E-4</v>
       </c>
       <c r="F17" s="1">
-        <v>2.1459885947653801</v>
+        <v>2.5836399590305201</v>
       </c>
       <c r="G17" s="1">
-        <v>41.589370255572703</v>
+        <v>40.207880360535</v>
       </c>
       <c r="H17" s="1">
-        <v>1.1334481937981999E-3</v>
+        <v>6.1506534392050496E-4</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="42.75">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B18" s="1">
-        <v>0.107638855603815</v>
+        <v>8.3337504828946599E-2</v>
       </c>
       <c r="C18" s="1">
-        <v>1.6481192218492899</v>
+        <v>1.6492623762916101</v>
       </c>
       <c r="D18" s="1">
-        <v>6.04689558055987E-4</v>
-      </c>
-      <c r="E18" s="1">
-        <v>-1.4610146508219399E-4</v>
+        <v>-2.24781195472006E-4</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1.8306766442070499E-5</v>
       </c>
       <c r="F18" s="1">
-        <v>2.6448507757386199</v>
+        <v>1.83576120363435</v>
       </c>
       <c r="G18" s="1">
-        <v>42.110862812159297</v>
+        <v>40.1084000089512</v>
       </c>
       <c r="H18" s="1">
-        <v>7.8479638618821101E-4</v>
+        <v>8.5995295316442703E-4</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="42.75">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B19" s="1">
-        <v>0.10699058330880699</v>
+        <v>8.4048471187493506E-2</v>
       </c>
       <c r="C19" s="1">
-        <v>1.6492623762916101</v>
+        <v>1.6487622651665801</v>
       </c>
       <c r="D19" s="1">
-        <v>-2.24781195472006E-4</v>
-      </c>
-      <c r="E19" s="2">
-        <v>1.8306766442070499E-5</v>
+        <v>4.3874674970470799E-4</v>
+      </c>
+      <c r="E19" s="1">
+        <v>-1.9927733135150199E-4</v>
       </c>
       <c r="F19" s="1">
-        <v>1.89697388484721</v>
+        <v>1.58388702956287</v>
       </c>
       <c r="G19" s="1">
-        <v>40.1917166038427</v>
+        <v>41.098285243438099</v>
       </c>
       <c r="H19" s="1">
-        <v>7.9828994241592198E-4</v>
+        <v>7.5220804955950698E-4</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="42.75">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B20" s="1">
-        <v>0.10798594921653699</v>
+        <v>8.3859299335631896E-2</v>
       </c>
       <c r="C20" s="1">
-        <v>1.6487622651665801</v>
+        <v>1.6471746969524299</v>
       </c>
       <c r="D20" s="1">
-        <v>4.3874674970470799E-4</v>
+        <v>3.6983539426320802E-4</v>
       </c>
       <c r="E20" s="1">
-        <v>-1.9927733135150199E-4</v>
+        <v>-1.37284784815389E-4</v>
       </c>
       <c r="F20" s="1">
-        <v>1.6450878247492799</v>
+        <v>1.8361132325795999</v>
       </c>
       <c r="G20" s="1">
-        <v>41.695269625295303</v>
+        <v>41.113379510201398</v>
       </c>
       <c r="H20" s="1">
-        <v>9.4514560402671102E-4</v>
+        <v>7.5220826802971396E-4</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="42.75">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B21" s="1">
-        <v>0.107583539743761</v>
+        <v>8.4150599797561301E-2</v>
       </c>
       <c r="C21" s="1">
-        <v>1.6471746969524299</v>
+        <v>1.6480888704369001</v>
       </c>
       <c r="D21" s="1">
-        <v>3.6983539426320802E-4</v>
+        <v>3.8121612932739599E-4</v>
       </c>
       <c r="E21" s="1">
-        <v>-1.37284784815389E-4</v>
+        <v>-1.4488331255244801E-4</v>
       </c>
       <c r="F21" s="1">
-        <v>1.89733966542986</v>
+        <v>1.8342170249071801</v>
       </c>
       <c r="G21" s="1">
-        <v>40.117406996777603</v>
+        <v>41.061210501596598</v>
       </c>
       <c r="H21" s="1">
-        <v>7.90480157218743E-4</v>
+        <v>7.5221035849676896E-4</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="42.75">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B22" s="1">
-        <v>0.108049349994359</v>
+        <v>8.3705403747337398E-2</v>
       </c>
       <c r="C22" s="1">
-        <v>1.6480888704369001</v>
+        <v>1.64709506847567</v>
       </c>
       <c r="D22" s="1">
-        <v>3.8121612932739599E-4</v>
+        <v>5.8463526041763799E-4</v>
       </c>
       <c r="E22" s="1">
-        <v>-1.4488331255244801E-4</v>
+        <v>-1.48800705440387E-4</v>
       </c>
       <c r="F22" s="1">
-        <v>1.89541269179618</v>
+        <v>2.3355196150598201</v>
       </c>
       <c r="G22" s="1">
-        <v>41.563812950561498</v>
+        <v>40.042568497555699</v>
       </c>
       <c r="H22" s="1">
-        <v>6.3614063364904696E-4</v>
+        <v>1.08939749563229E-3</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="42.75">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B23" s="1">
-        <v>0.107467389213943</v>
+        <v>8.38953398940607E-2</v>
       </c>
       <c r="C23" s="1">
-        <v>1.64709506847567</v>
+        <v>1.6467403108203</v>
       </c>
       <c r="D23" s="1">
-        <v>5.8463526041763799E-4</v>
+        <v>1.0863098043561901E-3</v>
       </c>
       <c r="E23" s="1">
-        <v>-1.48800705440387E-4</v>
+        <v>-2.4524586641952098E-4</v>
       </c>
       <c r="F23" s="1">
-        <v>2.3967461303469402</v>
+        <v>2.5839232106788699</v>
       </c>
       <c r="G23" s="1">
-        <v>40.266148497783703</v>
+        <v>41.018005009071601</v>
       </c>
       <c r="H23" s="1">
-        <v>1.0221795506426799E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="42.75">
-      <c r="A24" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" s="1">
-        <v>0.10771292800641501</v>
-      </c>
-      <c r="C24" s="1">
-        <v>1.6467403108203</v>
-      </c>
-      <c r="D24" s="1">
-        <v>1.0863098043561901E-3</v>
-      </c>
-      <c r="E24" s="1">
-        <v>-2.4524586641952098E-4</v>
-      </c>
-      <c r="F24" s="1">
-        <v>2.6451208221396398</v>
-      </c>
-      <c r="G24" s="1">
-        <v>41.018001576066197</v>
-      </c>
-      <c r="H24" s="1">
-        <v>7.5220731889189701E-4</v>
-      </c>
+        <v>7.5220783853681005E-4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1"/>
@@ -2017,10 +1998,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF8CB368-1F4F-4C65-B86B-93EC676CB77B}">
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2030,8 +2011,9 @@
       <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="42.75">
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="1:10" ht="42.75">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -2039,10 +2021,11 @@
         <v>5.2258479562069899</v>
       </c>
       <c r="C2" s="1">
-        <v>0.107867853594575</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="42.75">
+        <v>8.4098670481367904E-2</v>
+      </c>
+      <c r="J2" s="1"/>
+    </row>
+    <row r="3" spans="1:10" ht="42.75">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -2050,7 +2033,7 @@
         <v>5.1321123174082999</v>
       </c>
       <c r="C3" s="1">
-        <v>0.107552731189269</v>
+        <v>8.3770582022428597E-2</v>
       </c>
       <c r="G3">
         <v>894</v>
@@ -2058,8 +2041,9 @@
       <c r="H3">
         <v>456</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="42.75">
+      <c r="J3" s="1"/>
+    </row>
+    <row r="4" spans="1:10" ht="42.75">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -2067,7 +2051,7 @@
         <v>5.2437157298636796</v>
       </c>
       <c r="C4" s="1">
-        <v>0.10779387708665</v>
+        <v>8.3930571430078399E-2</v>
       </c>
       <c r="F4" t="s">
         <v>1</v>
@@ -2078,10 +2062,11 @@
       </c>
       <c r="H4">
         <f>AVERAGE(C2:C33)</f>
-        <v>0.10789991167356659</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="42.75">
+        <v>8.4028105692396882E-2</v>
+      </c>
+      <c r="J4" s="1"/>
+    </row>
+    <row r="5" spans="1:10" ht="42.75">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -2089,7 +2074,7 @@
         <v>5.2504871284328898</v>
       </c>
       <c r="C5" s="1">
-        <v>0.108339047437144</v>
+        <v>8.4386871474939104E-2</v>
       </c>
       <c r="F5" t="s">
         <v>2</v>
@@ -2100,10 +2085,11 @@
       </c>
       <c r="H5">
         <f>_xlfn.STDEV.S(C2:C33)</f>
-        <v>3.997083023183723E-4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="42.75">
+        <v>3.1432104335582978E-4</v>
+      </c>
+      <c r="J5" s="1"/>
+    </row>
+    <row r="6" spans="1:10" ht="42.75">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -2111,7 +2097,7 @@
         <v>5.2503356968257</v>
       </c>
       <c r="C6" s="1">
-        <v>0.107577120583375</v>
+        <v>8.3779094698236606E-2</v>
       </c>
       <c r="F6" t="s">
         <v>3</v>
@@ -2122,10 +2108,11 @@
       </c>
       <c r="H6">
         <f>H5/H4/SQRT(COUNT(C2:C33))</f>
-        <v>7.8978837948797569E-4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="42.75">
+        <v>7.9751258292580279E-4</v>
+      </c>
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" spans="1:10" ht="42.75">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -2133,10 +2120,11 @@
         <v>5.2336543988027202</v>
       </c>
       <c r="C7" s="1">
-        <v>0.108317067772985</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="42.75">
+        <v>8.4368245251587398E-2</v>
+      </c>
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:10" ht="42.75">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
@@ -2144,10 +2132,11 @@
         <v>5.2591832551717097</v>
       </c>
       <c r="C8" s="1">
-        <v>0.108753685676204</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="42.75">
+        <v>8.4640740114124396E-2</v>
+      </c>
+      <c r="J8" s="1"/>
+    </row>
+    <row r="9" spans="1:10" ht="42.75">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
@@ -2155,10 +2144,11 @@
         <v>5.2469052817766597</v>
       </c>
       <c r="C9" s="1">
-        <v>0.107673177325291</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="42.75">
+        <v>8.3819572528152295E-2</v>
+      </c>
+      <c r="J9" s="1"/>
+    </row>
+    <row r="10" spans="1:10" ht="42.75">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -2166,10 +2156,11 @@
         <v>5.25892843081182</v>
       </c>
       <c r="C10" s="1">
-        <v>0.108229705876452</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="42.75">
+        <v>8.4298501986348195E-2</v>
+      </c>
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="1:10" ht="42.75">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
@@ -2177,10 +2168,11 @@
         <v>5.21286007784256</v>
       </c>
       <c r="C11" s="1">
-        <v>0.10760496944564001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="42.75">
+        <v>8.3749879844150901E-2</v>
+      </c>
+      <c r="J11" s="1"/>
+    </row>
+    <row r="12" spans="1:10" ht="42.75">
       <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
@@ -2188,10 +2180,11 @@
         <v>5.2596778259212398</v>
       </c>
       <c r="C12" s="1">
-        <v>0.108210284447238</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="42.75">
+        <v>8.4288203419773597E-2</v>
+      </c>
+      <c r="J12" s="1"/>
+    </row>
+    <row r="13" spans="1:10" ht="42.75">
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
@@ -2199,10 +2192,11 @@
         <v>5.2590212289624798</v>
       </c>
       <c r="C13" s="1">
-        <v>0.108391645730674</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="42.75">
+        <v>8.4433783424020706E-2</v>
+      </c>
+      <c r="J13" s="1"/>
+    </row>
+    <row r="14" spans="1:10" ht="42.75">
       <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
@@ -2210,10 +2204,11 @@
         <v>5.2296998738747797</v>
       </c>
       <c r="C14" s="1">
-        <v>0.10781058117576001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="42.75">
+        <v>8.3978129655986694E-2</v>
+      </c>
+      <c r="J14" s="1"/>
+    </row>
+    <row r="15" spans="1:10" ht="42.75">
       <c r="A15" s="1" t="s">
         <v>24</v>
       </c>
@@ -2221,10 +2216,11 @@
         <v>5.2667771366869696</v>
       </c>
       <c r="C15" s="1">
-        <v>0.108326143627196</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="42.75">
+        <v>8.4391376865179599E-2</v>
+      </c>
+      <c r="J15" s="1"/>
+    </row>
+    <row r="16" spans="1:10" ht="42.75">
       <c r="A16" s="1" t="s">
         <v>25</v>
       </c>
@@ -2232,10 +2228,11 @@
         <v>5.2271473404603404</v>
       </c>
       <c r="C16" s="1">
-        <v>0.107921570762375</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="42.75">
+        <v>8.3986778727553404E-2</v>
+      </c>
+      <c r="J16" s="1"/>
+    </row>
+    <row r="17" spans="1:10" ht="42.75">
       <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
@@ -2243,10 +2240,11 @@
         <v>5.2172814151544804</v>
       </c>
       <c r="C17" s="1">
-        <v>0.107638855603815</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="42.75">
+        <v>8.3700704517771493E-2</v>
+      </c>
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="1:10" ht="42.75">
       <c r="A18" s="1" t="s">
         <v>27</v>
       </c>
@@ -2254,10 +2252,11 @@
         <v>5.2026205255307998</v>
       </c>
       <c r="C18" s="1">
-        <v>0.10699058330880699</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="42.75">
+        <v>8.3337504828946599E-2</v>
+      </c>
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="1:10" ht="42.75">
       <c r="A19" s="1" t="s">
         <v>28</v>
       </c>
@@ -2265,10 +2264,11 @@
         <v>5.2088502809019603</v>
       </c>
       <c r="C19" s="1">
-        <v>0.10798594921653699</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="42.75">
+        <v>8.4048471187493506E-2</v>
+      </c>
+      <c r="J19" s="1"/>
+    </row>
+    <row r="20" spans="1:10" ht="42.75">
       <c r="A20" s="1" t="s">
         <v>29</v>
       </c>
@@ -2276,10 +2276,11 @@
         <v>5.2306348705772896</v>
       </c>
       <c r="C20" s="1">
-        <v>0.107583539743761</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="42.75">
+        <v>8.3859299335631896E-2</v>
+      </c>
+      <c r="J20" s="1"/>
+    </row>
+    <row r="21" spans="1:10" ht="42.75">
       <c r="A21" s="1" t="s">
         <v>30</v>
       </c>
@@ -2287,10 +2288,11 @@
         <v>5.2252366536496302</v>
       </c>
       <c r="C21" s="1">
-        <v>0.108049349994359</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="42.75">
+        <v>8.4150599797561301E-2</v>
+      </c>
+      <c r="J21" s="1"/>
+    </row>
+    <row r="22" spans="1:10" ht="42.75">
       <c r="A22" s="1" t="s">
         <v>31</v>
       </c>
@@ -2298,10 +2300,11 @@
         <v>5.2416884024595696</v>
       </c>
       <c r="C22" s="1">
-        <v>0.107467389213943</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="42.75">
+        <v>8.3705403747337398E-2</v>
+      </c>
+      <c r="J22" s="1"/>
+    </row>
+    <row r="23" spans="1:10" ht="42.75">
       <c r="A23" s="1" t="s">
         <v>32</v>
       </c>
@@ -2309,73 +2312,61 @@
         <v>5.2293252887733699</v>
       </c>
       <c r="C23" s="1">
-        <v>0.10771292800641501</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
+        <v>8.38953398940607E-2</v>
+      </c>
+      <c r="J23" s="1"/>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-    </row>
-    <row r="25" spans="1:3">
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-    </row>
-    <row r="26" spans="1:3">
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-    </row>
-    <row r="27" spans="1:3">
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-    </row>
-    <row r="28" spans="1:3">
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-    </row>
-    <row r="29" spans="1:3">
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-    </row>
-    <row r="30" spans="1:3">
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-    </row>
-    <row r="31" spans="1:3">
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-    </row>
-    <row r="32" spans="1:3">
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-    </row>
-    <row r="33" spans="1:3">
+    </row>
+    <row r="33" spans="1:2">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-    </row>
-    <row r="34" spans="1:3">
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-    </row>
-    <row r="35" spans="1:3">
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-    </row>
-    <row r="36" spans="1:3">
+    </row>
+    <row r="36" spans="1:2">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/BeatnotePostHotCellF1=4/Jul14,2026/Fit_ResultJun14.xlsx
+++ b/BeatnotePostHotCellF1=4/Jul14,2026/Fit_ResultJun14.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\BeatnotePostHotCellF1=4\Jul14,2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{042E7298-5650-4423-B937-D6087930ECDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E71BBA-38D1-4AE4-8B46-0C93958E726B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{D9E101C5-8284-4B59-8B1C-2AD2D5F2FDD3}"/>
   </bookViews>
